--- a/data/raw/inventory/Week 27/White_Mulberry/Seller FBA Inventory (SP-API).xlsx
+++ b/data/raw/inventory/Week 27/White_Mulberry/Seller FBA Inventory (SP-API).xlsx
@@ -771,7 +771,7 @@
         <v>54</v>
       </c>
       <c r="F6" t="n">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
@@ -783,7 +783,7 @@
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K6" t="n">
         <v>54</v>
@@ -1760,10 +1760,10 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="F22" t="n">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="G22" t="n">
         <v>36</v>
@@ -1778,7 +1778,7 @@
         <v>19</v>
       </c>
       <c r="K22" t="n">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="L22" t="n">
         <v>4</v>
@@ -2135,7 +2135,7 @@
         <v>62</v>
       </c>
       <c r="F28" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G28" t="n">
         <v>8</v>
@@ -2147,7 +2147,7 @@
         <v>0</v>
       </c>
       <c r="J28" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K28" t="n">
         <v>78</v>
@@ -2259,7 +2259,7 @@
         <v>108</v>
       </c>
       <c r="F30" t="n">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
@@ -2271,7 +2271,7 @@
         <v>0</v>
       </c>
       <c r="J30" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K30" t="n">
         <v>115</v>
@@ -2584,10 +2584,10 @@
         <v>14</v>
       </c>
       <c r="K35" t="n">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="L35" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="M35" t="n">
         <v>1</v>

--- a/data/raw/inventory/Week 27/White_Mulberry/Seller FBA Inventory (SP-API).xlsx
+++ b/data/raw/inventory/Week 27/White_Mulberry/Seller FBA Inventory (SP-API).xlsx
@@ -768,10 +768,10 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F6" t="n">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
@@ -783,10 +783,10 @@
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K6" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="L6" t="n">
         <v>0</v>
@@ -833,7 +833,7 @@
         <v>37</v>
       </c>
       <c r="F7" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
@@ -845,7 +845,7 @@
         <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K7" t="n">
         <v>37</v>
@@ -892,7 +892,7 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F8" t="n">
         <v>53</v>
@@ -907,10 +907,10 @@
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
@@ -1016,10 +1016,10 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F10" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
@@ -1034,7 +1034,7 @@
         <v>1</v>
       </c>
       <c r="K10" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="L10" t="n">
         <v>2</v>
@@ -1202,7 +1202,7 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F13" t="n">
         <v>20</v>
@@ -1217,10 +1217,10 @@
         <v>0</v>
       </c>
       <c r="J13" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K13" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="L13" t="n">
         <v>0</v>
@@ -1636,10 +1636,10 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="F20" t="n">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
@@ -1651,10 +1651,10 @@
         <v>24</v>
       </c>
       <c r="J20" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K20" t="n">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="L20" t="n">
         <v>0</v>
@@ -1760,10 +1760,10 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="F22" t="n">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="G22" t="n">
         <v>36</v>
@@ -1778,7 +1778,7 @@
         <v>19</v>
       </c>
       <c r="K22" t="n">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="L22" t="n">
         <v>4</v>
@@ -2132,10 +2132,10 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="F28" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G28" t="n">
         <v>8</v>
@@ -2147,10 +2147,10 @@
         <v>0</v>
       </c>
       <c r="J28" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="K28" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="L28" t="n">
         <v>16</v>
@@ -2194,10 +2194,10 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F29" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
@@ -2212,7 +2212,7 @@
         <v>3</v>
       </c>
       <c r="K29" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="L29" t="n">
         <v>1</v>
@@ -2259,7 +2259,7 @@
         <v>108</v>
       </c>
       <c r="F30" t="n">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
@@ -2271,7 +2271,7 @@
         <v>0</v>
       </c>
       <c r="J30" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="K30" t="n">
         <v>115</v>
@@ -2321,7 +2321,7 @@
         <v>35</v>
       </c>
       <c r="F31" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G31" t="n">
         <v>6</v>
@@ -2333,7 +2333,7 @@
         <v>0</v>
       </c>
       <c r="J31" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K31" t="n">
         <v>41</v>
@@ -2566,10 +2566,10 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="F35" t="n">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
@@ -2581,13 +2581,13 @@
         <v>0</v>
       </c>
       <c r="J35" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="K35" t="n">
         <v>193</v>
       </c>
       <c r="L35" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="M35" t="n">
         <v>1</v>
